--- a/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
+++ b/downloads/indicadores/IMFBCF/IMFBCF_datos.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_10.pdf · Fecha de publicación: 5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -16978,7 +16978,7 @@
         <v>45566</v>
       </c>
       <c r="C387" s="7" t="n">
-        <v>109.22</v>
+        <v>113.1</v>
       </c>
       <c r="D387" s="7" t="n">
         <v>103.63</v>
@@ -17021,7 +17021,7 @@
         <v>45597</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>109.72</v>
+        <v>113.7</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>103.31</v>
@@ -17064,7 +17064,7 @@
         <v>45627</v>
       </c>
       <c r="C389" s="7" t="n">
-        <v>106.05</v>
+        <v>109.7</v>
       </c>
       <c r="D389" s="7" t="n">
         <v>101.16</v>
@@ -17107,7 +17107,7 @@
         <v>45658</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>105.18</v>
+        <v>107.4</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>100.32</v>
@@ -17150,7 +17150,7 @@
         <v>45689</v>
       </c>
       <c r="C391" s="7" t="n">
-        <v>106.05</v>
+        <v>107.3</v>
       </c>
       <c r="D391" s="7" t="n">
         <v>102.6</v>
@@ -17193,7 +17193,7 @@
         <v>45717</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>106.28</v>
+        <v>107.9</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>104.92</v>
@@ -17236,7 +17236,7 @@
         <v>45748</v>
       </c>
       <c r="C393" s="7" t="n">
-        <v>102.5</v>
+        <v>105.6</v>
       </c>
       <c r="D393" s="7" t="n">
         <v>100.02</v>
@@ -17279,7 +17279,7 @@
         <v>45778</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>105</v>
+        <v>106.8</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>104.33</v>
@@ -17322,7 +17322,7 @@
         <v>45809</v>
       </c>
       <c r="C395" s="7" t="n">
-        <v>103.03</v>
+        <v>105.6</v>
       </c>
       <c r="D395" s="7" t="n">
         <v>101.27</v>
@@ -17365,7 +17365,7 @@
         <v>45839</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>104.2</v>
+        <v>107.5</v>
       </c>
       <c r="D396" s="6" t="n">
         <v>101.13</v>
@@ -17408,7 +17408,7 @@
         <v>45870</v>
       </c>
       <c r="C397" s="7" t="n">
-        <v>101.76</v>
+        <v>103.9</v>
       </c>
       <c r="D397" s="7" t="n">
         <v>100.03</v>
@@ -17451,7 +17451,7 @@
         <v>45901</v>
       </c>
       <c r="C398" s="6" t="n">
-        <v>101.9</v>
+        <v>101</v>
       </c>
       <c r="D398" s="6" t="n">
         <v>98.06</v>
@@ -17494,7 +17494,7 @@
         <v>45931</v>
       </c>
       <c r="C399" s="7" t="n">
-        <v>102.91</v>
+        <v>102.2</v>
       </c>
       <c r="D399" s="7" t="n">
         <v>102.29</v>
@@ -17537,7 +17537,7 @@
         <v>45962</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>103.53</v>
+        <v>102.8</v>
       </c>
       <c r="D400" s="6" t="n">
         <v>103.9</v>
@@ -17580,7 +17580,7 @@
         <v>45992</v>
       </c>
       <c r="C401" s="7" t="n">
-        <v>104.02</v>
+        <v>103.6</v>
       </c>
       <c r="D401" s="7" t="n">
         <v>104.89</v>
@@ -17623,7 +17623,7 @@
         <v>46023</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>103.1</v>
+        <v>102.3</v>
       </c>
       <c r="D402" s="6" t="n">
         <v>103.91</v>
@@ -17666,7 +17666,7 @@
         <v>46054</v>
       </c>
       <c r="C403" s="7" t="n">
-        <v>102.79</v>
+        <v>101.1</v>
       </c>
       <c r="D403" s="7" t="n">
         <v>104.32</v>
@@ -17709,7 +17709,7 @@
         <v>46082</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>103.49</v>
+        <v>102</v>
       </c>
       <c r="D404" s="6" t="n">
         <v>102.18</v>
@@ -17752,7 +17752,7 @@
         <v>46113</v>
       </c>
       <c r="C405" s="7" t="n">
-        <v>107.99</v>
+        <v>107.4</v>
       </c>
       <c r="D405" s="7" t="n">
         <v>109.06</v>
@@ -17795,7 +17795,7 @@
         <v>46143</v>
       </c>
       <c r="C406" s="6" t="n">
-        <v>107.56</v>
+        <v>107.1</v>
       </c>
       <c r="D406" s="6" t="n">
         <v>106.32</v>
@@ -17838,7 +17838,7 @@
         <v>46174</v>
       </c>
       <c r="C407" s="7" t="n">
-        <v>109</v>
+        <v>108.7</v>
       </c>
       <c r="D407" s="7" t="n">
         <v>109.78</v>
@@ -17881,7 +17881,7 @@
         <v>46204</v>
       </c>
       <c r="C408" s="6" t="n">
-        <v>110.49</v>
+        <v>110.5</v>
       </c>
       <c r="D408" s="6" t="n">
         <v>108.1</v>
@@ -17961,7 +17961,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_10.pdf · Fecha de publicación: 5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -37606,10 +37606,10 @@
         <v>45566</v>
       </c>
       <c r="C387" s="9" t="n">
-        <v>-0.014793</v>
+        <v>0.001</v>
       </c>
       <c r="D387" s="9" t="n">
-        <v>-0.033964</v>
+        <v>-0.045</v>
       </c>
       <c r="E387" s="9" t="n">
         <v>-0.046467</v>
@@ -37624,10 +37624,10 @@
         <v>0.023328</v>
       </c>
       <c r="I387" s="9" t="n">
-        <v>-0.060483</v>
+        <v>-0.035</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.091243</v>
+        <v>-0.163</v>
       </c>
       <c r="K387" s="9" t="n">
         <v>0.000185</v>
@@ -37658,10 +37658,10 @@
         <v>45597</v>
       </c>
       <c r="C388" s="10" t="n">
-        <v>0.004578</v>
+        <v>0.001</v>
       </c>
       <c r="D388" s="10" t="n">
-        <v>-0.003813</v>
+        <v>-0.003</v>
       </c>
       <c r="E388" s="10" t="n">
         <v>-0.003088</v>
@@ -37676,10 +37676,10 @@
         <v>0.047653</v>
       </c>
       <c r="I388" s="10" t="n">
-        <v>0.046742</v>
+        <v>0.068</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>-0.112371</v>
+        <v>-0.148</v>
       </c>
       <c r="K388" s="10" t="n">
         <v>0.057605</v>
@@ -37710,10 +37710,10 @@
         <v>45627</v>
       </c>
       <c r="C389" s="9" t="n">
-        <v>-0.033449</v>
+        <v>-0.026</v>
       </c>
       <c r="D389" s="9" t="n">
-        <v>-0.050072</v>
+        <v>-0.041</v>
       </c>
       <c r="E389" s="9" t="n">
         <v>-0.020811</v>
@@ -37728,10 +37728,10 @@
         <v>-0.006558</v>
       </c>
       <c r="I389" s="9" t="n">
-        <v>0.014404</v>
+        <v>0.043</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>-0.149758</v>
+        <v>-0.171</v>
       </c>
       <c r="K389" s="9" t="n">
         <v>-0.0182</v>
@@ -37762,46 +37762,46 @@
         <v>45658</v>
       </c>
       <c r="C390" s="10" t="n">
-        <v>-0.008203999999999999</v>
+        <v>-0.015</v>
       </c>
       <c r="D390" s="10" t="n">
-        <v>-0.06515</v>
+        <v>-0.059</v>
       </c>
       <c r="E390" s="10" t="n">
-        <v>-0.008304000000000001</v>
+        <v>-0.014</v>
       </c>
       <c r="F390" s="10" t="n">
-        <v>-0.088828</v>
+        <v>-0.09</v>
       </c>
       <c r="G390" s="10" t="n">
-        <v>-0.010526</v>
+        <v>-0.018</v>
       </c>
       <c r="H390" s="10" t="n">
-        <v>-0.035394</v>
+        <v>-0.023</v>
       </c>
       <c r="I390" s="10" t="n">
-        <v>-0.017315</v>
+        <v>-0.014</v>
       </c>
       <c r="J390" s="10" t="n">
-        <v>-0.150826</v>
+        <v>-0.142</v>
       </c>
       <c r="K390" s="10" t="n">
-        <v>-0.064318</v>
+        <v>-0.031</v>
       </c>
       <c r="L390" s="10" t="n">
-        <v>-0.021607</v>
+        <v>0.022</v>
       </c>
       <c r="M390" s="10" t="n">
-        <v>-0.113942</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="N390" s="10" t="n">
-        <v>-0.019257</v>
+        <v>-0.016</v>
       </c>
       <c r="O390" s="10" t="n">
-        <v>-0.132589</v>
+        <v>-0.136</v>
       </c>
       <c r="P390" s="10" t="n">
-        <v>-0.004014</v>
+        <v>-0.001</v>
       </c>
     </row>
     <row r="391">
@@ -37814,46 +37814,46 @@
         <v>45689</v>
       </c>
       <c r="C391" s="9" t="n">
-        <v>0.008272</v>
+        <v>0.001</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.05683</v>
+        <v>-0.06</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>0.022727</v>
+        <v>0.017</v>
       </c>
       <c r="F391" s="9" t="n">
-        <v>-0.040494</v>
+        <v>-0.049</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.005319</v>
+        <v>-0.011</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.06626600000000001</v>
+        <v>-0.063</v>
       </c>
       <c r="I391" s="9" t="n">
-        <v>0.137153</v>
+        <v>0.128</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>-0.159093</v>
+        <v>-0.168</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>-0.047414</v>
+        <v>-0.021</v>
       </c>
       <c r="L391" s="9" t="n">
-        <v>-0.013395</v>
+        <v>0.021</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.08278099999999999</v>
+        <v>-0.077</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.081133</v>
+        <v>-0.093</v>
       </c>
       <c r="O391" s="9" t="n">
-        <v>-0.07638200000000001</v>
+        <v>-0.081</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.080456</v>
+        <v>-0.092</v>
       </c>
     </row>
     <row r="392">
@@ -37866,46 +37866,46 @@
         <v>45717</v>
       </c>
       <c r="C392" s="10" t="n">
-        <v>0.002169</v>
+        <v>0.003</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.049629</v>
+        <v>-0.047</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>0.022612</v>
+        <v>0.008</v>
       </c>
       <c r="F392" s="10" t="n">
-        <v>-0.022818</v>
+        <v>-0.031</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>-0.023475</v>
+        <v>-0.007</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.08438900000000001</v>
+        <v>-0.075</v>
       </c>
       <c r="I392" s="10" t="n">
-        <v>0.167823</v>
+        <v>0.147</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>-0.169774</v>
+        <v>-0.171</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>-0.088919</v>
+        <v>-0.066</v>
       </c>
       <c r="L392" s="10" t="n">
-        <v>-0.121711</v>
+        <v>-0.1</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.044447</v>
+        <v>-0.022</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.08330700000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="O392" s="10" t="n">
-        <v>-0.144131</v>
+        <v>-0.148</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.080375</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="393">
@@ -37918,46 +37918,46 @@
         <v>45748</v>
       </c>
       <c r="C393" s="9" t="n">
-        <v>-0.035566</v>
+        <v>-0.017</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.087591</v>
+        <v>-0.077</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.046702</v>
+        <v>-0.011</v>
       </c>
       <c r="F393" s="9" t="n">
-        <v>-0.072171</v>
+        <v>-0.055</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.019213</v>
+        <v>-0.022</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.09521399999999999</v>
+        <v>-0.091</v>
       </c>
       <c r="I393" s="9" t="n">
-        <v>-0.00257</v>
+        <v>0.024</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.132829</v>
+        <v>-0.118</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>-0.081099</v>
+        <v>-0.083</v>
       </c>
       <c r="L393" s="9" t="n">
-        <v>-0.149539</v>
+        <v>-0.143</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.01177</v>
+        <v>-0.019</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.098025</v>
+        <v>-0.091</v>
       </c>
       <c r="O393" s="9" t="n">
-        <v>-0.081844</v>
+        <v>-0.073</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.08964</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="394">
@@ -37970,46 +37970,46 @@
         <v>45778</v>
       </c>
       <c r="C394" s="10" t="n">
-        <v>0.02439</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.062667</v>
+        <v>-0.067</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>0.043091</v>
+        <v>0.014</v>
       </c>
       <c r="F394" s="10" t="n">
-        <v>-0.049298</v>
+        <v>-0.05</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>0.002839</v>
+        <v>0</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.075063</v>
+        <v>-0.082</v>
       </c>
       <c r="I394" s="10" t="n">
-        <v>0.088631</v>
+        <v>0.079</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>-0.187534</v>
+        <v>-0.171</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>-0.024414</v>
+        <v>-0.034</v>
       </c>
       <c r="L394" s="10" t="n">
-        <v>-0.064322</v>
+        <v>-0.055</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>0.028062</v>
+        <v>-0.019</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.103643</v>
+        <v>-0.106</v>
       </c>
       <c r="O394" s="10" t="n">
-        <v>-0.256319</v>
+        <v>-0.267</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.07158399999999999</v>
+        <v>-0.07199999999999999</v>
       </c>
     </row>
     <row r="395">
@@ -38022,46 +38022,46 @@
         <v>45809</v>
       </c>
       <c r="C395" s="9" t="n">
-        <v>-0.018762</v>
+        <v>-0.014</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.07230300000000001</v>
+        <v>-0.068</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.02933</v>
+        <v>-0.008</v>
       </c>
       <c r="F395" s="9" t="n">
-        <v>-0.050801</v>
+        <v>-0.033</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.010569</v>
+        <v>-0.016</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.106899</v>
+        <v>-0.114</v>
       </c>
       <c r="I395" s="9" t="n">
-        <v>0.122022</v>
+        <v>0.118</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>-0.17284</v>
+        <v>-0.138</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>-0.124258</v>
+        <v>-0.132</v>
       </c>
       <c r="L395" s="9" t="n">
-        <v>-0.164548</v>
+        <v>-0.155</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.08724899999999999</v>
+        <v>-0.114</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.09067</v>
+        <v>-0.096</v>
       </c>
       <c r="O395" s="9" t="n">
-        <v>-0.15206</v>
+        <v>-0.148</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.07466399999999999</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="396">
@@ -38074,46 +38074,46 @@
         <v>45839</v>
       </c>
       <c r="C396" s="10" t="n">
-        <v>0.011356</v>
+        <v>0.016</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.079017</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.001382</v>
+        <v>-0.013</v>
       </c>
       <c r="F396" s="10" t="n">
-        <v>-0.08529299999999999</v>
+        <v>-0.075</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>0.022794</v>
+        <v>0.049</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.065039</v>
+        <v>-0.059</v>
       </c>
       <c r="I396" s="10" t="n">
-        <v>0.041109</v>
+        <v>0.046</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>-0.187875</v>
+        <v>-0.176</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>-0.116425</v>
+        <v>-0.114</v>
       </c>
       <c r="L396" s="10" t="n">
-        <v>-0.181262</v>
+        <v>-0.172</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.049278</v>
+        <v>-0.049</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.025342</v>
+        <v>-0.015</v>
       </c>
       <c r="O396" s="10" t="n">
-        <v>-0.049277</v>
+        <v>-0.015</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.03036</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="397">
@@ -38126,46 +38126,46 @@
         <v>45870</v>
       </c>
       <c r="C397" s="9" t="n">
-        <v>-0.023417</v>
+        <v>-0.027</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.094178</v>
+        <v>-0.089</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.010877</v>
+        <v>-0.015</v>
       </c>
       <c r="F397" s="9" t="n">
-        <v>-0.070007</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.030586</v>
+        <v>-0.031</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.117637</v>
+        <v>-0.105</v>
       </c>
       <c r="I397" s="9" t="n">
-        <v>0.113232</v>
+        <v>0.1</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>-0.191035</v>
+        <v>-0.185</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>-0.125952</v>
+        <v>-0.092</v>
       </c>
       <c r="L397" s="9" t="n">
-        <v>-0.137324</v>
+        <v>-0.123</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.121397</v>
+        <v>-0.056</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.118583</v>
+        <v>-0.119</v>
       </c>
       <c r="O397" s="9" t="n">
-        <v>-0.153554</v>
+        <v>-0.154</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.108175</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="398">
@@ -38178,46 +38178,46 @@
         <v>45901</v>
       </c>
       <c r="C398" s="10" t="n">
-        <v>0.001376</v>
+        <v>-0.003</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.08082300000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.019694</v>
+        <v>-0.026</v>
       </c>
       <c r="F398" s="10" t="n">
-        <v>-0.097718</v>
+        <v>-0.102</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>0.017795</v>
+        <v>0.019</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.065118</v>
+        <v>-0.061</v>
       </c>
       <c r="I398" s="10" t="n">
-        <v>-0.014651</v>
+        <v>-0.02</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.161754</v>
+        <v>-0.164</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>-0.111466</v>
+        <v>-0.106</v>
       </c>
       <c r="L398" s="10" t="n">
-        <v>-0.172843</v>
+        <v>-0.168</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.045557</v>
+        <v>-0.04</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.033506</v>
+        <v>-0.033</v>
       </c>
       <c r="O398" s="10" t="n">
-        <v>-0.158776</v>
+        <v>-0.164</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.006236</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="399">
@@ -38230,46 +38230,46 @@
         <v>45931</v>
       </c>
       <c r="C399" s="9" t="n">
-        <v>0.009912000000000001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.057773</v>
+        <v>-0.058</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>0.043137</v>
+        <v>0.039</v>
       </c>
       <c r="F399" s="9" t="n">
-        <v>-0.012931</v>
+        <v>-0.016</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.022588</v>
+        <v>-0.022</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.106986</v>
+        <v>-0.103</v>
       </c>
       <c r="I399" s="9" t="n">
-        <v>0.123408</v>
+        <v>0.118</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>-0.119792</v>
+        <v>-0.126</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>-0.121344</v>
+        <v>-0.118</v>
       </c>
       <c r="L399" s="9" t="n">
-        <v>-0.172649</v>
+        <v>-0.171</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.053158</v>
+        <v>-0.047</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.097605</v>
+        <v>-0.094</v>
       </c>
       <c r="O399" s="9" t="n">
-        <v>-0.128095</v>
+        <v>-0.132</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.09198199999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -38282,46 +38282,46 @@
         <v>45962</v>
       </c>
       <c r="C400" s="10" t="n">
-        <v>0.006025</v>
+        <v>0.004</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.056416</v>
+        <v>-0.057</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>0.01574</v>
+        <v>0.015</v>
       </c>
       <c r="F400" s="10" t="n">
-        <v>0.005711</v>
+        <v>0.006</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>-0.000677</v>
+        <v>-0.002</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.118024</v>
+        <v>-0.116</v>
       </c>
       <c r="I400" s="10" t="n">
-        <v>0.093379</v>
+        <v>0.092</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>-0.067814</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>-0.153155</v>
+        <v>-0.152</v>
       </c>
       <c r="L400" s="10" t="n">
-        <v>-0.191512</v>
+        <v>-0.187</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.10334</v>
+        <v>-0.101</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.092404</v>
+        <v>-0.091</v>
       </c>
       <c r="O400" s="10" t="n">
-        <v>-0.186729</v>
+        <v>-0.191</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.07914</v>
+        <v>-0.075</v>
       </c>
     </row>
     <row r="401">
@@ -38334,46 +38334,46 @@
         <v>45992</v>
       </c>
       <c r="C401" s="9" t="n">
-        <v>0.004733</v>
+        <v>0.005</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.019142</v>
+        <v>-0.016</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>0.009528</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F401" s="9" t="n">
-        <v>0.036872</v>
+        <v>0.041</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>-9.7e-05</v>
+        <v>-0.003</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.07814500000000001</v>
+        <v>-0.079</v>
       </c>
       <c r="I401" s="9" t="n">
-        <v>0.140845</v>
+        <v>0.142</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>-0.032761</v>
+        <v>-0.03</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>-0.118167</v>
+        <v>-0.118</v>
       </c>
       <c r="L401" s="9" t="n">
-        <v>-0.166339</v>
+        <v>-0.163</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.054404</v>
+        <v>-0.053</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.050064</v>
+        <v>-0.049</v>
       </c>
       <c r="O401" s="9" t="n">
-        <v>-0.033403</v>
+        <v>-0.027</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.049462</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="402">
@@ -38386,46 +38386,46 @@
         <v>46023</v>
       </c>
       <c r="C402" s="10" t="n">
-        <v>-0.008843999999999999</v>
+        <v>-0.011</v>
       </c>
       <c r="D402" s="10" t="n">
-        <v>-0.019776</v>
+        <v>-0.022</v>
       </c>
       <c r="E402" s="10" t="n">
-        <v>-0.009343000000000001</v>
+        <v>-0.008</v>
       </c>
       <c r="F402" s="10" t="n">
-        <v>0.035785</v>
+        <v>0.038</v>
       </c>
       <c r="G402" s="10" t="n">
-        <v>-0.005129</v>
+        <v>-0.011</v>
       </c>
       <c r="H402" s="10" t="n">
-        <v>-0.073116</v>
+        <v>-0.08</v>
       </c>
       <c r="I402" s="10" t="n">
-        <v>0.079233</v>
+        <v>0.079</v>
       </c>
       <c r="J402" s="10" t="n">
-        <v>-0.001344</v>
+        <v>0</v>
       </c>
       <c r="K402" s="10" t="n">
-        <v>-0.103452</v>
+        <v>-0.111</v>
       </c>
       <c r="L402" s="10" t="n">
-        <v>-0.141162</v>
+        <v>-0.133</v>
       </c>
       <c r="M402" s="10" t="n">
-        <v>-0.069811</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="N402" s="10" t="n">
-        <v>-0.049172</v>
+        <v>-0.052</v>
       </c>
       <c r="O402" s="10" t="n">
-        <v>-0.037542</v>
+        <v>-0.036</v>
       </c>
       <c r="P402" s="10" t="n">
-        <v>-0.057035</v>
+        <v>-0.063</v>
       </c>
     </row>
     <row r="403">
@@ -38438,46 +38438,46 @@
         <v>46054</v>
       </c>
       <c r="C403" s="9" t="n">
-        <v>-0.003007</v>
+        <v>-0.008</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.03074</v>
+        <v>-0.036</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>0.003946</v>
+        <v>0.001</v>
       </c>
       <c r="F403" s="9" t="n">
-        <v>0.016764</v>
+        <v>0.015</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>-0.015271</v>
+        <v>-0.023</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>-0.082389</v>
+        <v>-0.091</v>
       </c>
       <c r="I403" s="9" t="n">
-        <v>0.019738</v>
+        <v>0.018</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.014078</v>
+        <v>0.01</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>-0.126646</v>
+        <v>-0.136</v>
       </c>
       <c r="L403" s="9" t="n">
-        <v>-0.192533</v>
+        <v>-0.193</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>-0.058835</v>
+        <v>-0.075</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.051289</v>
+        <v>-0.057</v>
       </c>
       <c r="O403" s="9" t="n">
-        <v>-0.148533</v>
+        <v>-0.149</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.037731</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="404">
@@ -38490,46 +38490,46 @@
         <v>46082</v>
       </c>
       <c r="C404" s="10" t="n">
-        <v>0.00681</v>
+        <v>0.004</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.026251</v>
+        <v>-0.031</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.020514</v>
+        <v>-0.024</v>
       </c>
       <c r="F404" s="10" t="n">
-        <v>-0.026115</v>
+        <v>-0.032</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>0.03309</v>
+        <v>0.031</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>-0.029237</v>
+        <v>-0.032</v>
       </c>
       <c r="I404" s="10" t="n">
-        <v>-0.08131099999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>0.033456</v>
+        <v>0.024</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.072573</v>
+        <v>-0.073</v>
       </c>
       <c r="L404" s="10" t="n">
-        <v>-0.127685</v>
+        <v>-0.131</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>-0.016816</v>
+        <v>-0.015</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>-0.012193</v>
+        <v>-0.016</v>
       </c>
       <c r="O404" s="10" t="n">
-        <v>0.066825</v>
+        <v>0.064</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.017227</v>
+        <v>-0.022</v>
       </c>
     </row>
     <row r="405">
@@ -38542,46 +38542,46 @@
         <v>46113</v>
       </c>
       <c r="C405" s="9" t="n">
-        <v>0.043482</v>
+        <v>0.04</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.053561</v>
+        <v>0.051</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>0.067332</v>
+        <v>0.065</v>
       </c>
       <c r="F405" s="9" t="n">
-        <v>0.090382</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.02266</v>
+        <v>0.02</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.012208</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="I405" s="9" t="n">
-        <v>0.168366</v>
+        <v>0.167</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.019608</v>
+        <v>0.011</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>-0.09908699999999999</v>
+        <v>-0.106</v>
       </c>
       <c r="L405" s="9" t="n">
-        <v>-0.075418</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>-0.11986</v>
+        <v>-0.124</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.086324</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="O405" s="9" t="n">
-        <v>-0.010483</v>
+        <v>-0.011</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.098373</v>
+        <v>0.098</v>
       </c>
     </row>
     <row r="406">
@@ -38594,46 +38594,46 @@
         <v>46143</v>
       </c>
       <c r="C406" s="10" t="n">
-        <v>-0.003982</v>
+        <v>-0.004</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.024381</v>
+        <v>0.024</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.025124</v>
+        <v>-0.024</v>
       </c>
       <c r="F406" s="10" t="n">
-        <v>0.019074</v>
+        <v>0.02</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.01739</v>
+        <v>0.015</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.026894</v>
+        <v>0.025</v>
       </c>
       <c r="I406" s="10" t="n">
-        <v>-0.051082</v>
+        <v>-0.054</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>0.107367</v>
+        <v>0.118</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>-0.07251199999999999</v>
+        <v>-0.077</v>
       </c>
       <c r="L406" s="10" t="n">
-        <v>-0.045689</v>
+        <v>-0.05</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>-0.089715</v>
+        <v>-0.091</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.08859300000000001</v>
+        <v>0.089</v>
       </c>
       <c r="O406" s="10" t="n">
-        <v>0.073911</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>0.096168</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="407">
@@ -38646,46 +38646,46 @@
         <v>46174</v>
       </c>
       <c r="C407" s="9" t="n">
-        <v>0.013388</v>
+        <v>0.013</v>
       </c>
       <c r="D407" s="9" t="n">
-        <v>0.057944</v>
+        <v>0.059</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>0.032543</v>
+        <v>0.035</v>
       </c>
       <c r="F407" s="9" t="n">
-        <v>0.084033</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G407" s="9" t="n">
-        <v>-0.010476</v>
+        <v>-0.011</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>0.026991</v>
+        <v>0.025</v>
       </c>
       <c r="I407" s="9" t="n">
-        <v>0.067426</v>
+        <v>0.067</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>0.09267</v>
+        <v>0.106</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>-0.032261</v>
+        <v>-0.034</v>
       </c>
       <c r="L407" s="9" t="n">
-        <v>-0.006429</v>
+        <v>-0.008</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>-0.058355</v>
+        <v>-0.06</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>0.06822300000000001</v>
+        <v>0.062</v>
       </c>
       <c r="O407" s="9" t="n">
-        <v>0.154844</v>
+        <v>0.157</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>0.05589</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="408">
@@ -38698,46 +38698,46 @@
         <v>46204</v>
       </c>
       <c r="C408" s="10" t="n">
-        <v>0.01367</v>
+        <v>0.014</v>
       </c>
       <c r="D408" s="10" t="n">
-        <v>0.060365</v>
+        <v>0.06</v>
       </c>
       <c r="E408" s="10" t="n">
-        <v>-0.015303</v>
+        <v>-0.015</v>
       </c>
       <c r="F408" s="10" t="n">
-        <v>0.068921</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G408" s="10" t="n">
-        <v>0.044948</v>
+        <v>0.045</v>
       </c>
       <c r="H408" s="10" t="n">
-        <v>0.049235</v>
+        <v>0.049</v>
       </c>
       <c r="I408" s="10" t="n">
-        <v>0.09245</v>
+        <v>0.092</v>
       </c>
       <c r="J408" s="10" t="n">
-        <v>0.040131</v>
+        <v>0.04</v>
       </c>
       <c r="K408" s="10" t="n">
-        <v>-0.030932</v>
+        <v>-0.031</v>
       </c>
       <c r="L408" s="10" t="n">
-        <v>-0.007579</v>
+        <v>-0.008</v>
       </c>
       <c r="M408" s="10" t="n">
-        <v>-0.05338</v>
+        <v>-0.053</v>
       </c>
       <c r="N408" s="10" t="n">
-        <v>0.09882299999999999</v>
+        <v>0.099</v>
       </c>
       <c r="O408" s="10" t="n">
-        <v>-0.079351</v>
+        <v>-0.079</v>
       </c>
       <c r="P408" s="10" t="n">
-        <v>0.139787</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -38788,7 +38788,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_10.pdf · Fecha de publicación: 5 de octubre de 2026</t>
         </is>
       </c>
     </row>
@@ -59632,19 +59632,19 @@
         <v>91.53</v>
       </c>
       <c r="J387" s="9" t="n">
-        <v>-0.045966</v>
+        <v>-0.029</v>
       </c>
       <c r="K387" s="9" t="n">
-        <v>0.03116</v>
+        <v>0.047</v>
       </c>
       <c r="L387" s="7" t="n">
         <v>125.59</v>
       </c>
       <c r="M387" s="9" t="n">
-        <v>-0.095564</v>
+        <v>-0.166</v>
       </c>
       <c r="N387" s="9" t="n">
-        <v>0.089361</v>
+        <v>0.034</v>
       </c>
       <c r="O387" s="7" t="n">
         <v>121.97</v>
@@ -59687,19 +59687,19 @@
         <v>97.25</v>
       </c>
       <c r="J388" s="10" t="n">
-        <v>0.059599</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K388" s="10" t="n">
-        <v>0.033895</v>
+        <v>0.049</v>
       </c>
       <c r="L388" s="6" t="n">
         <v>124.25</v>
       </c>
       <c r="M388" s="10" t="n">
-        <v>-0.111421</v>
+        <v>-0.147</v>
       </c>
       <c r="N388" s="10" t="n">
-        <v>0.067721</v>
+        <v>0.014</v>
       </c>
       <c r="O388" s="6" t="n">
         <v>121.22</v>
@@ -59742,19 +59742,19 @@
         <v>83.88</v>
       </c>
       <c r="J389" s="9" t="n">
-        <v>0.001074</v>
+        <v>0.032</v>
       </c>
       <c r="K389" s="9" t="n">
-        <v>0.031246</v>
+        <v>0.048</v>
       </c>
       <c r="L389" s="7" t="n">
         <v>134.91</v>
       </c>
       <c r="M389" s="9" t="n">
-        <v>-0.135026</v>
+        <v>-0.164</v>
       </c>
       <c r="N389" s="9" t="n">
-        <v>0.045963</v>
+        <v>-0.004</v>
       </c>
       <c r="O389" s="7" t="n">
         <v>116.23</v>
@@ -59834,46 +59834,46 @@
         <v>98.64</v>
       </c>
       <c r="D391" s="9" t="n">
-        <v>-0.080022</v>
+        <v>-0.078</v>
       </c>
       <c r="E391" s="9" t="n">
-        <v>-0.077477</v>
+        <v>-0.074</v>
       </c>
       <c r="F391" s="7" t="n">
         <v>94.59999999999999</v>
       </c>
       <c r="G391" s="9" t="n">
-        <v>-0.046755</v>
+        <v>-0.052</v>
       </c>
       <c r="H391" s="9" t="n">
-        <v>-0.07618</v>
+        <v>-0.079</v>
       </c>
       <c r="I391" s="7" t="n">
         <v>86.59999999999999</v>
       </c>
       <c r="J391" s="9" t="n">
-        <v>0.140825</v>
+        <v>0.141</v>
       </c>
       <c r="K391" s="9" t="n">
-        <v>0.050031</v>
+        <v>0.056</v>
       </c>
       <c r="L391" s="7" t="n">
         <v>103.42</v>
       </c>
       <c r="M391" s="9" t="n">
-        <v>-0.17211</v>
+        <v>-0.18</v>
       </c>
       <c r="N391" s="9" t="n">
-        <v>-0.166833</v>
+        <v>-0.174</v>
       </c>
       <c r="O391" s="7" t="n">
         <v>103.31</v>
       </c>
       <c r="P391" s="9" t="n">
-        <v>-0.113067</v>
+        <v>-0.104</v>
       </c>
       <c r="Q391" s="9" t="n">
-        <v>-0.078884</v>
+        <v>-0.06900000000000001</v>
       </c>
     </row>
     <row r="392">
@@ -59889,46 +59889,46 @@
         <v>105.87</v>
       </c>
       <c r="D392" s="10" t="n">
-        <v>-0.005915</v>
+        <v>-0.002</v>
       </c>
       <c r="E392" s="10" t="n">
-        <v>-0.053793</v>
+        <v>-0.049</v>
       </c>
       <c r="F392" s="6" t="n">
         <v>103.35</v>
       </c>
       <c r="G392" s="10" t="n">
-        <v>0.001356</v>
+        <v>-0.001</v>
       </c>
       <c r="H392" s="10" t="n">
-        <v>-0.050219</v>
+        <v>-0.05</v>
       </c>
       <c r="I392" s="6" t="n">
         <v>105.05</v>
       </c>
       <c r="J392" s="10" t="n">
-        <v>0.204564</v>
+        <v>0.205</v>
       </c>
       <c r="K392" s="10" t="n">
-        <v>0.103742</v>
+        <v>0.108</v>
       </c>
       <c r="L392" s="6" t="n">
         <v>101.47</v>
       </c>
       <c r="M392" s="10" t="n">
-        <v>-0.160156</v>
+        <v>-0.159</v>
       </c>
       <c r="N392" s="10" t="n">
-        <v>-0.164661</v>
+        <v>-0.164</v>
       </c>
       <c r="O392" s="6" t="n">
         <v>108.8</v>
       </c>
       <c r="P392" s="10" t="n">
-        <v>-0.013689</v>
+        <v>-0.004</v>
       </c>
       <c r="Q392" s="10" t="n">
-        <v>-0.057574</v>
+        <v>-0.047</v>
       </c>
     </row>
     <row r="393">
@@ -59944,46 +59944,46 @@
         <v>100.25</v>
       </c>
       <c r="D393" s="9" t="n">
-        <v>-0.131809</v>
+        <v>-0.125</v>
       </c>
       <c r="E393" s="9" t="n">
-        <v>-0.074395</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F393" s="7" t="n">
         <v>98.39</v>
       </c>
       <c r="G393" s="9" t="n">
-        <v>-0.100886</v>
+        <v>-0.092</v>
       </c>
       <c r="H393" s="9" t="n">
-        <v>-0.06349399999999999</v>
+        <v>-0.061</v>
       </c>
       <c r="I393" s="7" t="n">
         <v>92.01000000000001</v>
       </c>
       <c r="J393" s="9" t="n">
-        <v>-0.048008</v>
+        <v>-0.037</v>
       </c>
       <c r="K393" s="9" t="n">
-        <v>0.061543</v>
+        <v>0.067</v>
       </c>
       <c r="L393" s="7" t="n">
         <v>105.43</v>
       </c>
       <c r="M393" s="9" t="n">
-        <v>-0.146316</v>
+        <v>-0.139</v>
       </c>
       <c r="N393" s="9" t="n">
-        <v>-0.160082</v>
+        <v>-0.158</v>
       </c>
       <c r="O393" s="7" t="n">
         <v>102.39</v>
       </c>
       <c r="P393" s="9" t="n">
-        <v>-0.16389</v>
+        <v>-0.16</v>
       </c>
       <c r="Q393" s="9" t="n">
-        <v>-0.085881</v>
+        <v>-0.077</v>
       </c>
     </row>
     <row r="394">
@@ -59999,46 +59999,46 @@
         <v>107.78</v>
       </c>
       <c r="D394" s="10" t="n">
-        <v>-0.06594999999999999</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="E394" s="10" t="n">
-        <v>-0.072632</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F394" s="6" t="n">
         <v>108.65</v>
       </c>
       <c r="G394" s="10" t="n">
-        <v>-0.041634</v>
+        <v>-0.043</v>
       </c>
       <c r="H394" s="10" t="n">
-        <v>-0.058827</v>
+        <v>-0.058</v>
       </c>
       <c r="I394" s="6" t="n">
         <v>117.83</v>
       </c>
       <c r="J394" s="10" t="n">
-        <v>0.102451</v>
+        <v>0.096</v>
       </c>
       <c r="K394" s="10" t="n">
-        <v>0.07116500000000001</v>
+        <v>0.074</v>
       </c>
       <c r="L394" s="6" t="n">
         <v>98.54000000000001</v>
       </c>
       <c r="M394" s="10" t="n">
-        <v>-0.182241</v>
+        <v>-0.175</v>
       </c>
       <c r="N394" s="10" t="n">
-        <v>-0.164421</v>
+        <v>-0.162</v>
       </c>
       <c r="O394" s="6" t="n">
         <v>106.76</v>
       </c>
       <c r="P394" s="10" t="n">
-        <v>-0.093179</v>
+        <v>-0.103</v>
       </c>
       <c r="Q394" s="10" t="n">
-        <v>-0.087368</v>
+        <v>-0.082</v>
       </c>
     </row>
     <row r="395">
@@ -60054,46 +60054,46 @@
         <v>98.92</v>
       </c>
       <c r="D395" s="9" t="n">
-        <v>-0.068023</v>
+        <v>-0.064</v>
       </c>
       <c r="E395" s="9" t="n">
-        <v>-0.07188899999999999</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F395" s="7" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="G395" s="9" t="n">
-        <v>-0.04444</v>
+        <v>-0.032</v>
       </c>
       <c r="H395" s="9" t="n">
-        <v>-0.05654</v>
+        <v>-0.054</v>
       </c>
       <c r="I395" s="7" t="n">
         <v>87.73999999999999</v>
       </c>
       <c r="J395" s="9" t="n">
-        <v>0.127039</v>
+        <v>0.12</v>
       </c>
       <c r="K395" s="9" t="n">
-        <v>0.079336</v>
+        <v>0.082</v>
       </c>
       <c r="L395" s="7" t="n">
         <v>104.88</v>
       </c>
       <c r="M395" s="9" t="n">
-        <v>-0.161966</v>
+        <v>-0.137</v>
       </c>
       <c r="N395" s="9" t="n">
-        <v>-0.164006</v>
+        <v>-0.159</v>
       </c>
       <c r="O395" s="7" t="n">
         <v>102.41</v>
       </c>
       <c r="P395" s="9" t="n">
-        <v>-0.092432</v>
+        <v>-0.097</v>
       </c>
       <c r="Q395" s="9" t="n">
-        <v>-0.088196</v>
+        <v>-0.08400000000000001</v>
       </c>
     </row>
     <row r="396">
@@ -60109,46 +60109,46 @@
         <v>106.74</v>
       </c>
       <c r="D396" s="10" t="n">
-        <v>-0.068993</v>
+        <v>-0.066</v>
       </c>
       <c r="E396" s="10" t="n">
-        <v>-0.07146</v>
+        <v>-0.068</v>
       </c>
       <c r="F396" s="6" t="n">
         <v>102.77</v>
       </c>
       <c r="G396" s="10" t="n">
-        <v>-0.078957</v>
+        <v>-0.07199999999999999</v>
       </c>
       <c r="H396" s="10" t="n">
-        <v>-0.059907</v>
+        <v>-0.057</v>
       </c>
       <c r="I396" s="6" t="n">
         <v>99.95999999999999</v>
       </c>
       <c r="J396" s="10" t="n">
-        <v>0.058786</v>
+        <v>0.055</v>
       </c>
       <c r="K396" s="10" t="n">
-        <v>0.076241</v>
+        <v>0.078</v>
       </c>
       <c r="L396" s="6" t="n">
         <v>105.87</v>
       </c>
       <c r="M396" s="10" t="n">
-        <v>-0.188611</v>
+        <v>-0.172</v>
       </c>
       <c r="N396" s="10" t="n">
-        <v>-0.167692</v>
+        <v>-0.161</v>
       </c>
       <c r="O396" s="6" t="n">
         <v>111.33</v>
       </c>
       <c r="P396" s="10" t="n">
-        <v>-0.058122</v>
+        <v>-0.059</v>
       </c>
       <c r="Q396" s="10" t="n">
-        <v>-0.0838</v>
+        <v>-0.081</v>
       </c>
     </row>
     <row r="397">
@@ -60164,46 +60164,46 @@
         <v>102.22</v>
       </c>
       <c r="D397" s="9" t="n">
-        <v>-0.110434</v>
+        <v>-0.104</v>
       </c>
       <c r="E397" s="9" t="n">
-        <v>-0.076501</v>
+        <v>-0.073</v>
       </c>
       <c r="F397" s="7" t="n">
         <v>101.61</v>
       </c>
       <c r="G397" s="9" t="n">
-        <v>-0.07391499999999999</v>
+        <v>-0.074</v>
       </c>
       <c r="H397" s="9" t="n">
-        <v>-0.061709</v>
+        <v>-0.059</v>
       </c>
       <c r="I397" s="7" t="n">
         <v>91.92</v>
       </c>
       <c r="J397" s="9" t="n">
-        <v>0.09912700000000001</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K397" s="9" t="n">
-        <v>0.07893500000000001</v>
+        <v>0.079</v>
       </c>
       <c r="L397" s="7" t="n">
         <v>112.27</v>
       </c>
       <c r="M397" s="9" t="n">
-        <v>-0.189094</v>
+        <v>-0.179</v>
       </c>
       <c r="N397" s="9" t="n">
-        <v>-0.170628</v>
+        <v>-0.164</v>
       </c>
       <c r="O397" s="7" t="n">
         <v>102.94</v>
       </c>
       <c r="P397" s="9" t="n">
-        <v>-0.148693</v>
+        <v>-0.137</v>
       </c>
       <c r="Q397" s="9" t="n">
-        <v>-0.092241</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="398">
@@ -60219,46 +60219,46 @@
         <v>99.59</v>
       </c>
       <c r="D398" s="10" t="n">
-        <v>-0.067247</v>
+        <v>-0.067</v>
       </c>
       <c r="E398" s="10" t="n">
-        <v>-0.07550800000000001</v>
+        <v>-0.076</v>
       </c>
       <c r="F398" s="6" t="n">
         <v>94.42</v>
       </c>
       <c r="G398" s="10" t="n">
-        <v>-0.10832</v>
+        <v>-0.106</v>
       </c>
       <c r="H398" s="10" t="n">
-        <v>-0.066858</v>
+        <v>-0.067</v>
       </c>
       <c r="I398" s="6" t="n">
         <v>85.19</v>
       </c>
       <c r="J398" s="10" t="n">
-        <v>-0.028288</v>
+        <v>-0.031</v>
       </c>
       <c r="K398" s="10" t="n">
-        <v>0.06715500000000001</v>
+        <v>0.067</v>
       </c>
       <c r="L398" s="6" t="n">
         <v>104.59</v>
       </c>
       <c r="M398" s="10" t="n">
-        <v>-0.169591</v>
+        <v>-0.163</v>
       </c>
       <c r="N398" s="10" t="n">
-        <v>-0.170513</v>
+        <v>-0.171</v>
       </c>
       <c r="O398" s="6" t="n">
         <v>105.57</v>
       </c>
       <c r="P398" s="10" t="n">
-        <v>-0.020596</v>
+        <v>-0.024</v>
       </c>
       <c r="Q398" s="10" t="n">
-        <v>-0.084797</v>
+        <v>-0.08599999999999999</v>
       </c>
     </row>
     <row r="399">
@@ -60274,46 +60274,46 @@
         <v>107.9</v>
       </c>
       <c r="D399" s="9" t="n">
-        <v>-0.056241</v>
+        <v>-0.055</v>
       </c>
       <c r="E399" s="9" t="n">
-        <v>-0.07352300000000001</v>
+        <v>-0.074</v>
       </c>
       <c r="F399" s="7" t="n">
         <v>106.79</v>
       </c>
       <c r="G399" s="9" t="n">
-        <v>-0.008817999999999999</v>
+        <v>-0.007</v>
       </c>
       <c r="H399" s="9" t="n">
-        <v>-0.060994</v>
+        <v>-0.061</v>
       </c>
       <c r="I399" s="7" t="n">
         <v>103.82</v>
       </c>
       <c r="J399" s="9" t="n">
-        <v>0.134273</v>
+        <v>0.135</v>
       </c>
       <c r="K399" s="9" t="n">
-        <v>0.074062</v>
+        <v>0.074</v>
       </c>
       <c r="L399" s="7" t="n">
         <v>110.07</v>
       </c>
       <c r="M399" s="9" t="n">
-        <v>-0.123577</v>
+        <v>-0.122</v>
       </c>
       <c r="N399" s="9" t="n">
-        <v>-0.165838</v>
+        <v>-0.167</v>
       </c>
       <c r="O399" s="7" t="n">
         <v>109.17</v>
       </c>
       <c r="P399" s="9" t="n">
-        <v>-0.104944</v>
+        <v>-0.105</v>
       </c>
       <c r="Q399" s="9" t="n">
-        <v>-0.08691599999999999</v>
+        <v>-0.08799999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -60329,46 +60329,46 @@
         <v>107.74</v>
       </c>
       <c r="D400" s="10" t="n">
-        <v>-0.065163</v>
+        <v>-0.064</v>
       </c>
       <c r="E400" s="10" t="n">
-        <v>-0.072736</v>
+        <v>-0.073</v>
       </c>
       <c r="F400" s="6" t="n">
         <v>111.27</v>
       </c>
       <c r="G400" s="10" t="n">
-        <v>0.010627</v>
+        <v>0.013</v>
       </c>
       <c r="H400" s="10" t="n">
-        <v>-0.054291</v>
+        <v>-0.054</v>
       </c>
       <c r="I400" s="6" t="n">
         <v>107.18</v>
       </c>
       <c r="J400" s="10" t="n">
-        <v>0.102108</v>
+        <v>0.103</v>
       </c>
       <c r="K400" s="10" t="n">
-        <v>0.07682600000000001</v>
+        <v>0.077</v>
       </c>
       <c r="L400" s="6" t="n">
         <v>115.79</v>
       </c>
       <c r="M400" s="10" t="n">
-        <v>-0.068089</v>
+        <v>-0.065</v>
       </c>
       <c r="N400" s="10" t="n">
-        <v>-0.15707</v>
+        <v>-0.158</v>
       </c>
       <c r="O400" s="6" t="n">
         <v>103.66</v>
       </c>
       <c r="P400" s="10" t="n">
-        <v>-0.144861</v>
+        <v>-0.145</v>
       </c>
       <c r="Q400" s="10" t="n">
-        <v>-0.092401</v>
+        <v>-0.093</v>
       </c>
     </row>
     <row r="401">
@@ -60384,46 +60384,46 @@
         <v>111.63</v>
       </c>
       <c r="D401" s="9" t="n">
-        <v>-0.002413</v>
+        <v>0</v>
       </c>
       <c r="E401" s="9" t="n">
-        <v>-0.06684900000000001</v>
+        <v>-0.067</v>
       </c>
       <c r="F401" s="7" t="n">
         <v>112.38</v>
       </c>
       <c r="G401" s="9" t="n">
-        <v>0.03892</v>
+        <v>0.043</v>
       </c>
       <c r="H401" s="9" t="n">
-        <v>-0.046442</v>
+        <v>-0.046</v>
       </c>
       <c r="I401" s="7" t="n">
         <v>94.72</v>
       </c>
       <c r="J401" s="9" t="n">
-        <v>0.129232</v>
+        <v>0.133</v>
       </c>
       <c r="K401" s="9" t="n">
-        <v>0.080931</v>
+        <v>0.082</v>
       </c>
       <c r="L401" s="7" t="n">
         <v>131.83</v>
       </c>
       <c r="M401" s="9" t="n">
-        <v>-0.02283</v>
+        <v>-0.019</v>
       </c>
       <c r="N401" s="9" t="n">
-        <v>-0.145157</v>
+        <v>-0.146</v>
       </c>
       <c r="O401" s="7" t="n">
         <v>110.77</v>
       </c>
       <c r="P401" s="9" t="n">
-        <v>-0.046976</v>
+        <v>-0.046</v>
       </c>
       <c r="Q401" s="9" t="n">
-        <v>-0.08862100000000001</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="402">
@@ -60494,46 +60494,46 @@
         <v>94.67</v>
       </c>
       <c r="D403" s="9" t="n">
-        <v>-0.040247</v>
+        <v>-0.042</v>
       </c>
       <c r="E403" s="9" t="n">
-        <v>-0.036252</v>
+        <v>-0.037</v>
       </c>
       <c r="F403" s="7" t="n">
         <v>95.65000000000001</v>
       </c>
       <c r="G403" s="9" t="n">
-        <v>0.011099</v>
+        <v>0.011</v>
       </c>
       <c r="H403" s="9" t="n">
-        <v>0.019111</v>
+        <v>0.02</v>
       </c>
       <c r="I403" s="7" t="n">
         <v>88.31</v>
       </c>
       <c r="J403" s="9" t="n">
-        <v>0.019746</v>
+        <v>0.022</v>
       </c>
       <c r="K403" s="9" t="n">
-        <v>0.042644</v>
+        <v>0.045</v>
       </c>
       <c r="L403" s="7" t="n">
         <v>103.73</v>
       </c>
       <c r="M403" s="9" t="n">
-        <v>0.002997</v>
+        <v>0.001</v>
       </c>
       <c r="N403" s="9" t="n">
-        <v>-0.002395</v>
+        <v>-0.003</v>
       </c>
       <c r="O403" s="7" t="n">
         <v>93.53</v>
       </c>
       <c r="P403" s="9" t="n">
-        <v>-0.094667</v>
+        <v>-0.097</v>
       </c>
       <c r="Q403" s="9" t="n">
-        <v>-0.094289</v>
+        <v>-0.097</v>
       </c>
     </row>
     <row r="404">
@@ -60549,46 +60549,46 @@
         <v>103.31</v>
       </c>
       <c r="D404" s="10" t="n">
-        <v>-0.024181</v>
+        <v>-0.026</v>
       </c>
       <c r="E404" s="10" t="n">
-        <v>-0.032055</v>
+        <v>-0.033</v>
       </c>
       <c r="F404" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G404" s="10" t="n">
-        <v>-0.032414</v>
+        <v>-0.035</v>
       </c>
       <c r="H404" s="10" t="n">
-        <v>0.000922</v>
+        <v>0</v>
       </c>
       <c r="I404" s="6" t="n">
         <v>95.81999999999999</v>
       </c>
       <c r="J404" s="10" t="n">
-        <v>-0.087863</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="K404" s="10" t="n">
-        <v>-0.006861</v>
+        <v>-0.007</v>
       </c>
       <c r="L404" s="6" t="n">
         <v>104.6</v>
       </c>
       <c r="M404" s="10" t="n">
-        <v>0.030847</v>
+        <v>0.024</v>
       </c>
       <c r="N404" s="10" t="n">
-        <v>0.008477999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="O404" s="6" t="n">
         <v>107.14</v>
       </c>
       <c r="P404" s="10" t="n">
-        <v>-0.015257</v>
+        <v>-0.015</v>
       </c>
       <c r="Q404" s="10" t="n">
-        <v>-0.06725399999999999</v>
+        <v>-0.068</v>
       </c>
     </row>
     <row r="405">
@@ -60604,46 +60604,46 @@
         <v>106.31</v>
       </c>
       <c r="D405" s="9" t="n">
-        <v>0.060449</v>
+        <v>0.059</v>
       </c>
       <c r="E405" s="9" t="n">
-        <v>-0.009142000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F405" s="7" t="n">
         <v>108.56</v>
       </c>
       <c r="G405" s="9" t="n">
-        <v>0.103364</v>
+        <v>0.101</v>
       </c>
       <c r="H405" s="9" t="n">
-        <v>0.02669</v>
+        <v>0.026</v>
       </c>
       <c r="I405" s="7" t="n">
         <v>108.88</v>
       </c>
       <c r="J405" s="9" t="n">
-        <v>0.18335</v>
+        <v>0.185</v>
       </c>
       <c r="K405" s="9" t="n">
-        <v>0.040575</v>
+        <v>0.041</v>
       </c>
       <c r="L405" s="7" t="n">
         <v>108.2</v>
       </c>
       <c r="M405" s="9" t="n">
-        <v>0.026273</v>
+        <v>0.02</v>
       </c>
       <c r="N405" s="9" t="n">
-        <v>0.012992</v>
+        <v>0.012</v>
       </c>
       <c r="O405" s="7" t="n">
         <v>103.71</v>
       </c>
       <c r="P405" s="9" t="n">
-        <v>0.012892</v>
+        <v>0.013</v>
       </c>
       <c r="Q405" s="9" t="n">
-        <v>-0.047736</v>
+        <v>-0.048</v>
       </c>
     </row>
     <row r="406">
@@ -60659,46 +60659,46 @@
         <v>108.89</v>
       </c>
       <c r="D406" s="10" t="n">
-        <v>0.010299</v>
+        <v>0.011</v>
       </c>
       <c r="E406" s="10" t="n">
-        <v>-0.005054</v>
+        <v>-0.005</v>
       </c>
       <c r="F406" s="6" t="n">
         <v>111.32</v>
       </c>
       <c r="G406" s="10" t="n">
-        <v>0.024574</v>
+        <v>0.027</v>
       </c>
       <c r="H406" s="10" t="n">
-        <v>0.02623</v>
+        <v>0.027</v>
       </c>
       <c r="I406" s="6" t="n">
         <v>112.5</v>
       </c>
       <c r="J406" s="10" t="n">
-        <v>-0.045235</v>
+        <v>-0.047</v>
       </c>
       <c r="K406" s="10" t="n">
-        <v>0.019804</v>
+        <v>0.019</v>
       </c>
       <c r="L406" s="6" t="n">
         <v>110.01</v>
       </c>
       <c r="M406" s="10" t="n">
-        <v>0.116399</v>
+        <v>0.124</v>
       </c>
       <c r="N406" s="10" t="n">
-        <v>0.032809</v>
+        <v>0.034</v>
       </c>
       <c r="O406" s="6" t="n">
         <v>106.07</v>
       </c>
       <c r="P406" s="10" t="n">
-        <v>-0.006463</v>
+        <v>-0.007</v>
       </c>
       <c r="Q406" s="10" t="n">
-        <v>-0.039378</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="407">
@@ -60714,46 +60714,46 @@
         <v>106.27</v>
       </c>
       <c r="D407" s="9" t="n">
-        <v>0.07430200000000001</v>
+        <v>0.077</v>
       </c>
       <c r="E407" s="9" t="n">
-        <v>0.007785</v>
+        <v>0.008</v>
       </c>
       <c r="F407" s="7" t="n">
         <v>104.3</v>
       </c>
       <c r="G407" s="9" t="n">
-        <v>0.087591</v>
+        <v>0.092</v>
       </c>
       <c r="H407" s="9" t="n">
-        <v>0.036108</v>
+        <v>0.037</v>
       </c>
       <c r="I407" s="7" t="n">
         <v>93.92</v>
       </c>
       <c r="J407" s="9" t="n">
-        <v>0.070435</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K407" s="9" t="n">
-        <v>0.027536</v>
+        <v>0.028</v>
       </c>
       <c r="L407" s="7" t="n">
         <v>115.74</v>
       </c>
       <c r="M407" s="9" t="n">
-        <v>0.103547</v>
+        <v>0.111</v>
       </c>
       <c r="N407" s="9" t="n">
-        <v>0.044793</v>
+        <v>0.046</v>
       </c>
       <c r="O407" s="7" t="n">
         <v>108.55</v>
       </c>
       <c r="P407" s="9" t="n">
-        <v>0.059955</v>
+        <v>0.06</v>
       </c>
       <c r="Q407" s="9" t="n">
-        <v>-0.023221</v>
+        <v>-0.023</v>
       </c>
     </row>
     <row r="408">
@@ -60769,46 +60769,46 @@
         <v>113.83</v>
       </c>
       <c r="D408" s="10" t="n">
-        <v>0.066423</v>
+        <v>0.066</v>
       </c>
       <c r="E408" s="10" t="n">
-        <v>0.0165</v>
+        <v>0.017</v>
       </c>
       <c r="F408" s="6" t="n">
         <v>110.04</v>
       </c>
       <c r="G408" s="10" t="n">
-        <v>0.07074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H408" s="10" t="n">
-        <v>0.041204</v>
+        <v>0.041</v>
       </c>
       <c r="I408" s="6" t="n">
         <v>110.51</v>
       </c>
       <c r="J408" s="10" t="n">
-        <v>0.105542</v>
+        <v>0.106</v>
       </c>
       <c r="K408" s="10" t="n">
-        <v>0.039097</v>
+        <v>0.039</v>
       </c>
       <c r="L408" s="6" t="n">
         <v>109.53</v>
       </c>
       <c r="M408" s="10" t="n">
-        <v>0.034571</v>
+        <v>0.035</v>
       </c>
       <c r="N408" s="10" t="n">
-        <v>0.0433</v>
+        <v>0.043</v>
       </c>
       <c r="O408" s="6" t="n">
         <v>118.21</v>
       </c>
       <c r="P408" s="10" t="n">
-        <v>0.061798</v>
+        <v>0.062</v>
       </c>
       <c r="Q408" s="10" t="n">
-        <v>-0.010446</v>
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>
@@ -60845,7 +60845,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_09.pdf · Fecha de publicación: 4 de septiembre de 2026</t>
+          <t>Fuente: Banco de México (SIE) / INEGI · Frecuencia: Mensual · Unidad: índice base 2018=100 / % · Boletín: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_10.pdf · Fecha de publicación: 5 de octubre de 2026</t>
         </is>
       </c>
     </row>
